--- a/docs/sample-output/13-data-center/estimate.xlsx
+++ b/docs/sample-output/13-data-center/estimate.xlsx
@@ -16,12 +16,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="719" uniqueCount="376">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="725" uniqueCount="381">
   <si>
     <t>FINISHES SOLUTIONS</t>
   </si>
   <si>
-    <t>Total Project Cost — Summary   ·   Ashburn Campus — 24 MW data center · Total $493,856,922</t>
+    <t>Total Project Cost — Summary   ·   Ashburn Campus — 24 MW data center · Total $493,631,983</t>
   </si>
   <si>
     <t>COST SUMMARY</t>
@@ -90,7 +90,7 @@
     <t>Research data version</t>
   </si>
   <si>
-    <t>2026.7c60a42879</t>
+    <t>2026.0c737c8255</t>
   </si>
   <si>
     <t>Engine</t>
@@ -99,10 +99,10 @@
     <t>budget-engine-2.0.0</t>
   </si>
   <si>
-    <t>All defaults come from the research data shipped with the app (2026.7c60a42879), escalated to the construction midpoint and adjusted to the project location. Values marked "Derived estimate — verify" have no direct published source.</t>
-  </si>
-  <si>
-    <t>Cost by Component   ·   Ashburn Campus — 24 MW data center · Total $493,856,922</t>
+    <t>All defaults come from the research data shipped with the app (2026.0c737c8255), escalated to the construction midpoint and adjusted to the project location. Values marked "Derived estimate — verify" have no direct published source.</t>
+  </si>
+  <si>
+    <t>Cost by Component   ·   Ashburn Campus — 24 MW data center · Total $493,631,983</t>
   </si>
   <si>
     <t>Component</t>
@@ -147,7 +147,7 @@
     <t>within ($9,500–$24,000)</t>
   </si>
   <si>
-    <t>Cost by Phase   ·   Ashburn Campus — 24 MW data center · Total $493,856,922</t>
+    <t>Cost by Phase   ·   Ashburn Campus — 24 MW data center · Total $493,631,983</t>
   </si>
   <si>
     <t>Phase</t>
@@ -189,7 +189,7 @@
     <t>8.0%</t>
   </si>
   <si>
-    <t>Line-Item Detail   ·   Ashburn Campus — 24 MW data center · Total $493,856,922</t>
+    <t>Line-Item Detail   ·   Ashburn Campus — 24 MW data center · Total $493,631,983</t>
   </si>
   <si>
     <t>Group</t>
@@ -438,7 +438,7 @@
     <t>TOTAL</t>
   </si>
   <si>
-    <t>Draw Schedules   ·   Ashburn Campus — 24 MW data center · Total $493,856,922</t>
+    <t>Draw Schedules   ·   Ashburn Campus — 24 MW data center · Total $493,631,983</t>
   </si>
   <si>
     <t>PHASE 1 — MONTHLY DRAWS</t>
@@ -540,7 +540,7 @@
     <t>2029-08</t>
   </si>
   <si>
-    <t>Sources &amp; Assumptions   ·   Ashburn Campus — 24 MW data center · Total $493,856,922</t>
+    <t>Sources &amp; Assumptions   ·   Ashburn Campus — 24 MW data center · Total $493,631,983</t>
   </si>
   <si>
     <t>ASSUMPTIONS</t>
@@ -576,7 +576,7 @@
     <t>LTC 60%, rate 7.00%, fee 1.00%</t>
   </si>
   <si>
-    <t>SOURCES (49)</t>
+    <t>SOURCES (50)</t>
   </si>
   <si>
     <t>Ref</t>
@@ -1144,6 +1144,21 @@
   </si>
   <si>
     <t>https://www.nextmsc.com/industry-deep-dive/data-centre-cost-per-mw-by-region</t>
+  </si>
+  <si>
+    <t>residential/single-family.json#e10</t>
+  </si>
+  <si>
+    <t>Cost of Constructing a Home-2024 (Special Study for Housing Economics)</t>
+  </si>
+  <si>
+    <t>National Association of Home Builders (Eric Lynch)</t>
+  </si>
+  <si>
+    <t>26747 USD/unit (2024)</t>
+  </si>
+  <si>
+    <t>https://nahb.org/-/media/AB4EFC742624475A97A0A62189986FF8.ashx</t>
   </si>
 </sst>
 </file>
@@ -1733,7 +1748,7 @@
         <v>7</v>
       </c>
       <c r="B9" s="5">
-        <v>40991382.32</v>
+        <v>40991382.32000001</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
@@ -1741,7 +1756,7 @@
         <v>8</v>
       </c>
       <c r="B10" s="5">
-        <v>1896049.44</v>
+        <v>1707684.48</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
@@ -1749,7 +1764,7 @@
         <v>9</v>
       </c>
       <c r="B11" s="5">
-        <v>17034022.57</v>
+        <v>17025885.2</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
@@ -1757,7 +1772,7 @@
         <v>10</v>
       </c>
       <c r="B12" s="5">
-        <v>20332335.19</v>
+        <v>20318967.67</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
@@ -1765,7 +1780,7 @@
         <v>11</v>
       </c>
       <c r="B13" s="5">
-        <v>3367194.54</v>
+        <v>3352125.34</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
@@ -1773,7 +1788,7 @@
         <v>12</v>
       </c>
       <c r="B14" s="7">
-        <v>83620984.06</v>
+        <v>83396045.01</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
@@ -1789,7 +1804,7 @@
         <v>14</v>
       </c>
       <c r="B16" s="7">
-        <v>493856921.96</v>
+        <v>493631982.91</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
@@ -1828,7 +1843,7 @@
         <v>22</v>
       </c>
       <c r="B21" s="5">
-        <v>30866057.6225</v>
+        <v>30851998.931875</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
@@ -1956,19 +1971,19 @@
         <v>379595937.9</v>
       </c>
       <c r="E5" s="13">
-        <v>83620984.06</v>
+        <v>83396045.01</v>
       </c>
       <c r="F5" s="13">
         <v>30640000</v>
       </c>
       <c r="G5" s="13">
-        <v>493856921.96</v>
+        <v>493631982.91</v>
       </c>
       <c r="H5" s="13">
-        <v>20577.37174833333</v>
+        <v>20567.999287916668</v>
       </c>
       <c r="I5" s="14">
-        <v>1714.7809790277777</v>
+        <v>1713.9999406597224</v>
       </c>
       <c r="J5" s="12" t="s">
         <v>42</v>
@@ -1984,13 +1999,13 @@
         <v>379595937.9</v>
       </c>
       <c r="E6" s="16">
-        <v>83620984.06</v>
+        <v>83396045.01</v>
       </c>
       <c r="F6" s="16">
         <v>30640000</v>
       </c>
       <c r="G6" s="16">
-        <v>493856921.96</v>
+        <v>493631982.91</v>
       </c>
       <c r="H6" s="15"/>
       <c r="I6" s="15"/>
@@ -2106,19 +2121,19 @@
         <v>379595937.9</v>
       </c>
       <c r="G5" s="13">
-        <v>83620984.06</v>
+        <v>83396045.01</v>
       </c>
       <c r="H5" s="13">
         <v>30640000</v>
       </c>
       <c r="I5" s="13">
-        <v>493856921.96</v>
+        <v>493631982.91</v>
       </c>
       <c r="J5" s="13">
-        <v>296314153.18</v>
+        <v>296179189.75</v>
       </c>
       <c r="K5" s="13">
-        <v>17369193.66</v>
+        <v>17357175.77</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
@@ -2133,13 +2148,13 @@
         <v>379595937.9</v>
       </c>
       <c r="G6" s="16">
-        <v>83620984.06</v>
+        <v>83396045.01</v>
       </c>
       <c r="H6" s="16">
         <v>30640000</v>
       </c>
       <c r="I6" s="16">
-        <v>493856921.96</v>
+        <v>493631982.91</v>
       </c>
       <c r="J6" s="15"/>
       <c r="K6" s="15"/>
@@ -3164,10 +3179,10 @@
         <v>124</v>
       </c>
       <c r="H36" s="14">
-        <v>4838.18</v>
+        <v>3407.22</v>
       </c>
       <c r="I36" s="13">
-        <v>348348.96</v>
+        <v>245319.84</v>
       </c>
       <c r="J36" s="12" t="s">
         <v>69</v>
@@ -3196,10 +3211,10 @@
         <v>124</v>
       </c>
       <c r="H37" s="14">
-        <v>4592.44</v>
+        <v>3407.22</v>
       </c>
       <c r="I37" s="13">
-        <v>330655.68</v>
+        <v>245319.84</v>
       </c>
       <c r="J37" s="12" t="s">
         <v>69</v>
@@ -3229,7 +3244,7 @@
       </c>
       <c r="H38" s="18"/>
       <c r="I38" s="13">
-        <v>3367194.54</v>
+        <v>3352125.34</v>
       </c>
       <c r="J38" s="12" t="s">
         <v>69</v>
@@ -3375,7 +3390,7 @@
       </c>
       <c r="H43" s="18"/>
       <c r="I43" s="13">
-        <v>17034022.57</v>
+        <v>17025885.2</v>
       </c>
       <c r="J43" s="12" t="s">
         <v>69</v>
@@ -3403,7 +3418,7 @@
       </c>
       <c r="H44" s="18"/>
       <c r="I44" s="13">
-        <v>17369193.66</v>
+        <v>17357175.77</v>
       </c>
       <c r="J44" s="12" t="s">
         <v>69</v>
@@ -3431,7 +3446,7 @@
       </c>
       <c r="H45" s="18"/>
       <c r="I45" s="13">
-        <v>2963141.53</v>
+        <v>2961791.9</v>
       </c>
       <c r="J45" s="12" t="s">
         <v>69</v>
@@ -3451,7 +3466,7 @@
       <c r="G46" s="15"/>
       <c r="H46" s="15"/>
       <c r="I46" s="16">
-        <v>493856921.96</v>
+        <v>493631982.91</v>
       </c>
       <c r="J46" s="15"/>
     </row>
@@ -3550,13 +3565,13 @@
         <v>0</v>
       </c>
       <c r="C6" s="13">
-        <v>25302936.16</v>
+        <v>25114571.2</v>
       </c>
       <c r="D6" s="13">
         <v>30640000</v>
       </c>
       <c r="E6" s="13">
-        <v>58906077.69</v>
+        <v>58716363.1</v>
       </c>
       <c r="F6" s="13">
         <v>0</v>
@@ -3576,13 +3591,13 @@
         <v>1112603.84</v>
       </c>
       <c r="C7" s="13">
-        <v>1309852.17</v>
+        <v>1309051.94</v>
       </c>
       <c r="D7" s="13">
         <v>0</v>
       </c>
       <c r="E7" s="13">
-        <v>2422456.01</v>
+        <v>2421655.78</v>
       </c>
       <c r="F7" s="13">
         <v>0</v>
@@ -3602,13 +3617,13 @@
         <v>3324767.22</v>
       </c>
       <c r="C8" s="13">
-        <v>1309852.17</v>
+        <v>1309051.94</v>
       </c>
       <c r="D8" s="13">
         <v>0</v>
       </c>
       <c r="E8" s="13">
-        <v>4634619.39</v>
+        <v>4633819.16</v>
       </c>
       <c r="F8" s="13">
         <v>0</v>
@@ -3628,13 +3643,13 @@
         <v>5497950.75</v>
       </c>
       <c r="C9" s="13">
-        <v>1309852.17</v>
+        <v>1309051.94</v>
       </c>
       <c r="D9" s="13">
         <v>0</v>
       </c>
       <c r="E9" s="13">
-        <v>6807802.92</v>
+        <v>6807002.69</v>
       </c>
       <c r="F9" s="13">
         <v>0</v>
@@ -3654,13 +3669,13 @@
         <v>7606675.83</v>
       </c>
       <c r="C10" s="13">
-        <v>1309852.17</v>
+        <v>1309051.94</v>
       </c>
       <c r="D10" s="13">
         <v>0</v>
       </c>
       <c r="E10" s="13">
-        <v>8916528</v>
+        <v>8915727.77</v>
       </c>
       <c r="F10" s="13">
         <v>0</v>
@@ -3680,13 +3695,13 @@
         <v>9626219.63</v>
       </c>
       <c r="C11" s="13">
-        <v>1309852.17</v>
+        <v>1309051.94</v>
       </c>
       <c r="D11" s="13">
         <v>0</v>
       </c>
       <c r="E11" s="13">
-        <v>10936071.8</v>
+        <v>10935271.57</v>
       </c>
       <c r="F11" s="13">
         <v>0</v>
@@ -3706,13 +3721,13 @@
         <v>11532904.76</v>
       </c>
       <c r="C12" s="13">
-        <v>1309852.17</v>
+        <v>1309051.94</v>
       </c>
       <c r="D12" s="13">
         <v>0</v>
       </c>
       <c r="E12" s="13">
-        <v>12842756.93</v>
+        <v>12841956.7</v>
       </c>
       <c r="F12" s="13">
         <v>0</v>
@@ -3732,13 +3747,13 @@
         <v>13304377.15</v>
       </c>
       <c r="C13" s="13">
-        <v>1309852.17</v>
+        <v>1309051.94</v>
       </c>
       <c r="D13" s="13">
         <v>0</v>
       </c>
       <c r="E13" s="13">
-        <v>14614229.32</v>
+        <v>14613429.09</v>
       </c>
       <c r="F13" s="13">
         <v>0</v>
@@ -3758,13 +3773,13 @@
         <v>14919867.82</v>
       </c>
       <c r="C14" s="13">
-        <v>1309852.17</v>
+        <v>1309051.94</v>
       </c>
       <c r="D14" s="13">
         <v>0</v>
       </c>
       <c r="E14" s="13">
-        <v>16229719.99</v>
+        <v>16228919.76</v>
       </c>
       <c r="F14" s="13">
         <v>0</v>
@@ -3784,13 +3799,13 @@
         <v>16360436.78</v>
       </c>
       <c r="C15" s="13">
-        <v>1309852.17</v>
+        <v>1309051.94</v>
       </c>
       <c r="D15" s="13">
         <v>0</v>
       </c>
       <c r="E15" s="13">
-        <v>17670288.95</v>
+        <v>17669488.72</v>
       </c>
       <c r="F15" s="13">
         <v>0</v>
@@ -3810,13 +3825,13 @@
         <v>17609194.51</v>
       </c>
       <c r="C16" s="13">
-        <v>1309852.17</v>
+        <v>1309051.94</v>
       </c>
       <c r="D16" s="13">
         <v>0</v>
       </c>
       <c r="E16" s="13">
-        <v>18919046.68</v>
+        <v>18918246.45</v>
       </c>
       <c r="F16" s="13">
         <v>0</v>
@@ -3836,13 +3851,13 @@
         <v>18651500.58</v>
       </c>
       <c r="C17" s="13">
-        <v>1309852.16</v>
+        <v>1309051.94</v>
       </c>
       <c r="D17" s="13">
         <v>0</v>
       </c>
       <c r="E17" s="13">
-        <v>19961352.74</v>
+        <v>19960552.52</v>
       </c>
       <c r="F17" s="13">
         <v>0</v>
@@ -3862,22 +3877,22 @@
         <v>19475134.85</v>
       </c>
       <c r="C18" s="13">
-        <v>1309852.17</v>
+        <v>1309051.94</v>
       </c>
       <c r="D18" s="13">
         <v>0</v>
       </c>
       <c r="E18" s="13">
-        <v>4681818.36</v>
+        <v>4790359.85</v>
       </c>
       <c r="F18" s="13">
-        <v>16103168.66</v>
+        <v>15993826.94</v>
       </c>
       <c r="G18" s="13">
         <v>0</v>
       </c>
       <c r="H18" s="13">
-        <v>16103168.66</v>
+        <v>15993826.94</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
@@ -3888,7 +3903,7 @@
         <v>20070440.94</v>
       </c>
       <c r="C19" s="13">
-        <v>1309852.17</v>
+        <v>1309051.94</v>
       </c>
       <c r="D19" s="13">
         <v>0</v>
@@ -3897,13 +3912,13 @@
         <v>0</v>
       </c>
       <c r="F19" s="13">
-        <v>21380293.11</v>
+        <v>21379492.88</v>
       </c>
       <c r="G19" s="13">
-        <v>93935.15</v>
+        <v>93297.32</v>
       </c>
       <c r="H19" s="13">
-        <v>37577396.92</v>
+        <v>37466617.14</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
@@ -3914,7 +3929,7 @@
         <v>20430439.45</v>
       </c>
       <c r="C20" s="13">
-        <v>1309852.17</v>
+        <v>1309051.94</v>
       </c>
       <c r="D20" s="13">
         <v>0</v>
@@ -3923,13 +3938,13 @@
         <v>0</v>
       </c>
       <c r="F20" s="13">
-        <v>21740291.62</v>
+        <v>21739491.39</v>
       </c>
       <c r="G20" s="13">
-        <v>219201.48</v>
+        <v>218555.27</v>
       </c>
       <c r="H20" s="13">
-        <v>59536890.02</v>
+        <v>59424663.8</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
@@ -3940,7 +3955,7 @@
         <v>20550909.76</v>
       </c>
       <c r="C21" s="13">
-        <v>1309852.17</v>
+        <v>1309051.94</v>
       </c>
       <c r="D21" s="13">
         <v>0</v>
@@ -3949,13 +3964,13 @@
         <v>0</v>
       </c>
       <c r="F21" s="13">
-        <v>21860761.93</v>
+        <v>21859961.7</v>
       </c>
       <c r="G21" s="13">
-        <v>347298.53</v>
+        <v>346643.87</v>
       </c>
       <c r="H21" s="13">
-        <v>81744950.48</v>
+        <v>81631269.37</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
@@ -3966,7 +3981,7 @@
         <v>20430439.45</v>
       </c>
       <c r="C22" s="13">
-        <v>1309852.16</v>
+        <v>1309051.94</v>
       </c>
       <c r="D22" s="13">
         <v>0</v>
@@ -3975,13 +3990,13 @@
         <v>0</v>
       </c>
       <c r="F22" s="13">
-        <v>21740291.61</v>
+        <v>21739491.39</v>
       </c>
       <c r="G22" s="13">
-        <v>476845.54</v>
+        <v>476182.4</v>
       </c>
       <c r="H22" s="13">
-        <v>103962087.63</v>
+        <v>103846943.16</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
@@ -3992,7 +4007,7 @@
         <v>20070440.9</v>
       </c>
       <c r="C23" s="13">
-        <v>1309852.16</v>
+        <v>1309051.94</v>
       </c>
       <c r="D23" s="13">
         <v>0</v>
@@ -4001,13 +4016,13 @@
         <v>0</v>
       </c>
       <c r="F23" s="13">
-        <v>21380293.06</v>
+        <v>21379492.84</v>
       </c>
       <c r="G23" s="13">
-        <v>606445.51</v>
+        <v>605773.84</v>
       </c>
       <c r="H23" s="13">
-        <v>125948826.2</v>
+        <v>125832209.84</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
@@ -4018,7 +4033,7 @@
         <v>19475134.85</v>
       </c>
       <c r="C24" s="13">
-        <v>1309852.17</v>
+        <v>1309051.94</v>
       </c>
       <c r="D24" s="13">
         <v>0</v>
@@ -4027,13 +4042,13 @@
         <v>0</v>
       </c>
       <c r="F24" s="13">
-        <v>20784987.02</v>
+        <v>20784186.79</v>
       </c>
       <c r="G24" s="13">
-        <v>734701.49</v>
+        <v>734021.22</v>
       </c>
       <c r="H24" s="13">
-        <v>147468514.71</v>
+        <v>147350417.85</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
@@ -4044,7 +4059,7 @@
         <v>18651500.58</v>
       </c>
       <c r="C25" s="13">
-        <v>1309852.16</v>
+        <v>1309051.94</v>
       </c>
       <c r="D25" s="13">
         <v>0</v>
@@ -4053,13 +4068,13 @@
         <v>0</v>
       </c>
       <c r="F25" s="13">
-        <v>19961352.74</v>
+        <v>19960552.52</v>
       </c>
       <c r="G25" s="13">
-        <v>860233</v>
+        <v>859544.1</v>
       </c>
       <c r="H25" s="13">
-        <v>168290100.45</v>
+        <v>168170514.47</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
@@ -4070,7 +4085,7 @@
         <v>17609194.5</v>
       </c>
       <c r="C26" s="13">
-        <v>1309852.17</v>
+        <v>1309051.94</v>
       </c>
       <c r="D26" s="13">
         <v>0</v>
@@ -4079,13 +4094,13 @@
         <v>0</v>
       </c>
       <c r="F26" s="13">
-        <v>18919046.67</v>
+        <v>18918246.44</v>
       </c>
       <c r="G26" s="13">
-        <v>981692.25</v>
+        <v>980994.67</v>
       </c>
       <c r="H26" s="13">
-        <v>188190839.37</v>
+        <v>188069755.58</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
@@ -4096,7 +4111,7 @@
         <v>16360436.76</v>
       </c>
       <c r="C27" s="13">
-        <v>1309852.16</v>
+        <v>1309051.94</v>
       </c>
       <c r="D27" s="13">
         <v>0</v>
@@ -4105,13 +4120,13 @@
         <v>0</v>
       </c>
       <c r="F27" s="13">
-        <v>17670288.92</v>
+        <v>17669488.7</v>
       </c>
       <c r="G27" s="13">
-        <v>1097779.9</v>
+        <v>1097073.57</v>
       </c>
       <c r="H27" s="13">
-        <v>206958908.19</v>
+        <v>206836317.85</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
@@ -4122,7 +4137,7 @@
         <v>14919867.81</v>
       </c>
       <c r="C28" s="13">
-        <v>1309852.16</v>
+        <v>1309051.94</v>
       </c>
       <c r="D28" s="13">
         <v>0</v>
@@ -4131,13 +4146,13 @@
         <v>0</v>
       </c>
       <c r="F28" s="13">
-        <v>16229719.97</v>
+        <v>16228919.75</v>
       </c>
       <c r="G28" s="13">
-        <v>1207260.3</v>
+        <v>1206545.19</v>
       </c>
       <c r="H28" s="13">
-        <v>224395888.46</v>
+        <v>224271782.79</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
@@ -4148,7 +4163,7 @@
         <v>13304377.15</v>
       </c>
       <c r="C29" s="13">
-        <v>1309852.17</v>
+        <v>1309051.94</v>
       </c>
       <c r="D29" s="13">
         <v>0</v>
@@ -4157,13 +4172,13 @@
         <v>0</v>
       </c>
       <c r="F29" s="13">
-        <v>14614229.32</v>
+        <v>14613429.09</v>
       </c>
       <c r="G29" s="13">
-        <v>1308976.02</v>
+        <v>1308252.07</v>
       </c>
       <c r="H29" s="13">
-        <v>240319093.8</v>
+        <v>240193463.95</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
@@ -4174,7 +4189,7 @@
         <v>11532904.76</v>
       </c>
       <c r="C30" s="13">
-        <v>1309852.15</v>
+        <v>1309051.94</v>
       </c>
       <c r="D30" s="13">
         <v>0</v>
@@ -4183,13 +4198,13 @@
         <v>0</v>
       </c>
       <c r="F30" s="13">
-        <v>12842756.91</v>
+        <v>12841956.7</v>
       </c>
       <c r="G30" s="13">
-        <v>1401861.38</v>
+        <v>1401128.54</v>
       </c>
       <c r="H30" s="13">
-        <v>254563712.09</v>
+        <v>254436549.19</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
@@ -4200,7 +4215,7 @@
         <v>9626219.63</v>
       </c>
       <c r="C31" s="13">
-        <v>1309852.14</v>
+        <v>1309051.92</v>
       </c>
       <c r="D31" s="13">
         <v>0</v>
@@ -4209,13 +4224,13 @@
         <v>0</v>
       </c>
       <c r="F31" s="13">
-        <v>10936071.77</v>
+        <v>10935271.55</v>
       </c>
       <c r="G31" s="13">
-        <v>1484954.99</v>
+        <v>1484213.2</v>
       </c>
       <c r="H31" s="13">
-        <v>266984738.85</v>
+        <v>266856033.94</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
@@ -4226,7 +4241,7 @@
         <v>7606675.83</v>
       </c>
       <c r="C32" s="13">
-        <v>1309852.17</v>
+        <v>1309051.94</v>
       </c>
       <c r="D32" s="13">
         <v>0</v>
@@ -4235,13 +4250,13 @@
         <v>0</v>
       </c>
       <c r="F32" s="13">
-        <v>8916528</v>
+        <v>8915727.77</v>
       </c>
       <c r="G32" s="13">
-        <v>1557410.98</v>
+        <v>1556660.2</v>
       </c>
       <c r="H32" s="13">
-        <v>277458677.83</v>
+        <v>277328421.91</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
@@ -4252,7 +4267,7 @@
         <v>5497950.75</v>
       </c>
       <c r="C33" s="13">
-        <v>1309852.13</v>
+        <v>1309051.91</v>
       </c>
       <c r="D33" s="13">
         <v>0</v>
@@ -4261,13 +4276,13 @@
         <v>0</v>
       </c>
       <c r="F33" s="13">
-        <v>6807802.88</v>
+        <v>6807002.66</v>
       </c>
       <c r="G33" s="13">
-        <v>1618508.95</v>
+        <v>1617749.13</v>
       </c>
       <c r="H33" s="13">
-        <v>285884989.66</v>
+        <v>285753173.7</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
@@ -4278,7 +4293,7 @@
         <v>3324767.22</v>
       </c>
       <c r="C34" s="13">
-        <v>1309852.17</v>
+        <v>1309051.94</v>
       </c>
       <c r="D34" s="13">
         <v>0</v>
@@ -4287,13 +4302,13 @@
         <v>0</v>
       </c>
       <c r="F34" s="13">
-        <v>4634619.39</v>
+        <v>4633819.16</v>
       </c>
       <c r="G34" s="13">
-        <v>1667662.44</v>
+        <v>1666893.51</v>
       </c>
       <c r="H34" s="13">
-        <v>292187271.49</v>
+        <v>292053886.37</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
@@ -4304,7 +4319,7 @@
         <v>1112603.84</v>
       </c>
       <c r="C35" s="13">
-        <v>1309852.1</v>
+        <v>1309051.87</v>
       </c>
       <c r="D35" s="13">
         <v>0</v>
@@ -4313,13 +4328,13 @@
         <v>0</v>
       </c>
       <c r="F35" s="13">
-        <v>2422455.94</v>
+        <v>2421655.71</v>
       </c>
       <c r="G35" s="13">
-        <v>1704425.75</v>
+        <v>1703647.67</v>
       </c>
       <c r="H35" s="13">
-        <v>296314153.18</v>
+        <v>296179189.75</v>
       </c>
     </row>
   </sheetData>
@@ -4341,7 +4356,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F60"/>
+  <dimension ref="A1:F61"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="34" customWidth="1"/>
@@ -5426,6 +5441,26 @@
       </c>
       <c r="F60" s="12" t="s">
         <v>375</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A61" s="11" t="s">
+        <v>376</v>
+      </c>
+      <c r="B61" s="12" t="s">
+        <v>377</v>
+      </c>
+      <c r="C61" s="12" t="s">
+        <v>378</v>
+      </c>
+      <c r="D61" s="12" t="s">
+        <v>379</v>
+      </c>
+      <c r="E61" s="12" t="s">
+        <v>221</v>
+      </c>
+      <c r="F61" s="12" t="s">
+        <v>380</v>
       </c>
     </row>
   </sheetData>
